--- a/site/exports/muc-management.xlsx
+++ b/site/exports/muc-management.xlsx
@@ -817,7 +817,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L3" s="2" t="b">
@@ -888,7 +888,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L4" s="2" t="b">
@@ -955,7 +955,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L5" s="2" t="b">
